--- a/data/trans_bre/IP19C01-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP19C01-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-20,86; 3,78</t>
+          <t>-20,14; 3,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 20,75</t>
+          <t>-3,41; 21,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-27,24; -1,7</t>
+          <t>-25,53; -0,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-17,74; 6,39</t>
+          <t>-16,48; 6,87</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-26,7; 6,07</t>
+          <t>-26,78; 5,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-5,34; 34,23</t>
+          <t>-4,55; 36,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-32,34; -2,31</t>
+          <t>-30,64; -1,71</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-19,42; 8,07</t>
+          <t>-18,08; 8,26</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-14,43; 5,02</t>
+          <t>-15,04; 4,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-23,54; -5,47</t>
+          <t>-24,0; -4,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-11,94; 7,04</t>
+          <t>-12,38; 7,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 16,49</t>
+          <t>0,07; 16,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-18,87; 7,56</t>
+          <t>-19,68; 7,16</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-29,18; -7,01</t>
+          <t>-29,14; -6,28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-15,84; 10,24</t>
+          <t>-15,89; 10,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 22,44</t>
+          <t>0,22; 22,97</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,28; 9,67</t>
+          <t>-13,79; 9,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,37; 14,56</t>
+          <t>-7,71; 13,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 16,49</t>
+          <t>-5,17; 16,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-20,86; 1,57</t>
+          <t>-19,47; 3,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-16,78; 14,97</t>
+          <t>-17,32; 13,75</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-10,61; 22,58</t>
+          <t>-10,12; 20,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-7,2; 25,27</t>
+          <t>-6,62; 24,96</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-25,11; 1,83</t>
+          <t>-23,19; 4,7</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-17,75; 7,28</t>
+          <t>-18,14; 4,93</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-17,42; 2,75</t>
+          <t>-16,94; 3,55</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-11,35; 7,69</t>
+          <t>-10,59; 8,09</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-8,16; 8,23</t>
+          <t>-7,85; 8,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-23,98; 11,12</t>
+          <t>-23,89; 7,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-20,29; 3,27</t>
+          <t>-19,51; 4,39</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-13,39; 10,49</t>
+          <t>-12,56; 10,79</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-8,99; 9,86</t>
+          <t>-8,58; 10,63</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,68; 0,12</t>
+          <t>-11,19; 0,11</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,99; 1,63</t>
+          <t>-9,38; 0,99</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,57; 2,89</t>
+          <t>-7,32; 3,1</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,42; 4,52</t>
+          <t>-5,38; 4,11</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,6; 0,12</t>
+          <t>-15,04; 0,17</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,43; 2,29</t>
+          <t>-11,88; 1,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-9,64; 3,96</t>
+          <t>-9,33; 4,2</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,43; 5,69</t>
+          <t>-6,28; 5,12</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C01-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP19C01-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-20,14; 3,84</t>
+          <t>-19,58; 4,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 21,25</t>
+          <t>-3,18; 20,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-25,53; -0,7</t>
+          <t>-26,15; -2,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-16,48; 6,87</t>
+          <t>-17,15; 7,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-26,78; 5,74</t>
+          <t>-25,79; 6,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 36,09</t>
+          <t>-4,37; 35,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-30,64; -1,71</t>
+          <t>-31,41; -3,6</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-18,08; 8,26</t>
+          <t>-18,99; 9,26</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-15,04; 4,73</t>
+          <t>-15,63; 4,77</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-24,0; -4,65</t>
+          <t>-22,8; -3,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-12,38; 7,42</t>
+          <t>-11,91; 7,42</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,07; 16,49</t>
+          <t>-0,89; 15,68</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-19,68; 7,16</t>
+          <t>-20,08; 7,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-29,14; -6,28</t>
+          <t>-27,64; -5,28</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-15,89; 10,82</t>
+          <t>-15,66; 10,87</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,22; 22,97</t>
+          <t>-1,01; 21,04</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,79; 9,24</t>
+          <t>-13,31; 9,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 13,77</t>
+          <t>-8,81; 14,23</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 16,37</t>
+          <t>-5,29; 16,3</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-19,47; 3,46</t>
+          <t>-21,4; 2,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-17,32; 13,75</t>
+          <t>-16,89; 14,83</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-10,12; 20,91</t>
+          <t>-11,62; 21,52</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 24,96</t>
+          <t>-6,59; 25,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-23,19; 4,7</t>
+          <t>-25,1; 3,93</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-18,14; 4,93</t>
+          <t>-16,82; 6,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-16,94; 3,55</t>
+          <t>-17,34; 1,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-10,59; 8,09</t>
+          <t>-11,6; 7,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,85; 8,67</t>
+          <t>-7,24; 8,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-23,89; 7,85</t>
+          <t>-22,78; 10,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-19,51; 4,39</t>
+          <t>-20,15; 2,37</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-12,56; 10,79</t>
+          <t>-13,54; 10,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-8,58; 10,63</t>
+          <t>-8,0; 10,23</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,19; 0,11</t>
+          <t>-10,88; -0,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,38; 0,99</t>
+          <t>-9,08; 1,67</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 3,1</t>
+          <t>-7,85; 2,65</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 4,11</t>
+          <t>-5,83; 3,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-15,04; 0,17</t>
+          <t>-14,73; -0,15</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,88; 1,32</t>
+          <t>-11,64; 2,24</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-9,33; 4,2</t>
+          <t>-9,8; 3,68</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 5,12</t>
+          <t>-7,0; 4,86</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C01-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP19C01-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-5,26</t>
+          <t>-5,84</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-6,09%</t>
+          <t>-6,71%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-19,58; 4,16</t>
+          <t>-20,86; 3,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,18; 20,95</t>
+          <t>-3,67; 20,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-26,15; -2,39</t>
+          <t>-27,24; -1,7</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-17,15; 7,57</t>
+          <t>-17,91; 5,59</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-25,79; 6,7</t>
+          <t>-26,7; 6,07</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 35,53</t>
+          <t>-5,34; 34,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-31,41; -3,6</t>
+          <t>-32,34; -2,31</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-18,99; 9,26</t>
+          <t>-19,7; 6,77</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,87</t>
+          <t>7,36</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>9,32%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-15,63; 4,77</t>
+          <t>-14,43; 5,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-22,8; -3,82</t>
+          <t>-23,54; -5,47</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-11,91; 7,42</t>
+          <t>-11,94; 7,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 15,68</t>
+          <t>-1,09; 16,04</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-20,08; 7,21</t>
+          <t>-18,87; 7,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-27,64; -5,28</t>
+          <t>-29,18; -7,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-15,66; 10,87</t>
+          <t>-15,84; 10,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-1,01; 21,04</t>
+          <t>-1,19; 21,8</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-8,81</t>
+          <t>-7,56</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-10,97%</t>
+          <t>-9,53%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-13,31; 9,74</t>
+          <t>-13,28; 9,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,81; 14,23</t>
+          <t>-8,37; 14,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 16,3</t>
+          <t>-5,69; 16,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-21,4; 2,94</t>
+          <t>-18,97; 2,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-16,89; 14,83</t>
+          <t>-16,78; 14,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-11,62; 21,52</t>
+          <t>-10,61; 22,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 25,08</t>
+          <t>-7,2; 25,27</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-25,1; 3,93</t>
+          <t>-22,79; 3,08</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,09</t>
+          <t>-0,7</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,11%</t>
+          <t>-0,8%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-16,82; 6,84</t>
+          <t>-17,75; 7,28</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-17,34; 1,96</t>
+          <t>-17,42; 2,75</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-11,6; 7,92</t>
+          <t>-11,35; 7,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-7,24; 8,58</t>
+          <t>-8,96; 7,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-22,78; 10,56</t>
+          <t>-23,98; 11,12</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-20,15; 2,37</t>
+          <t>-20,29; 3,27</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-13,54; 10,26</t>
+          <t>-13,39; 10,49</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-8,0; 10,23</t>
+          <t>-9,95; 8,64</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-0,74</t>
+          <t>-0,69</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-0,9%</t>
+          <t>-0,84%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,88; -0,03</t>
+          <t>-10,68; 0,12</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-9,08; 1,67</t>
+          <t>-8,99; 1,63</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,85; 2,65</t>
+          <t>-7,57; 2,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 3,9</t>
+          <t>-5,21; 4,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-14,73; -0,15</t>
+          <t>-14,6; 0,12</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-11,64; 2,24</t>
+          <t>-11,43; 2,29</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-9,8; 3,68</t>
+          <t>-9,64; 3,96</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-7,0; 4,86</t>
+          <t>-6,15; 5,87</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP19C01-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/IP19C01-Habitat-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-7,87</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>9,26</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-13,16</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-5,84</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-11,17%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>14,0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-16,43%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-6,71%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-7.865857996795755</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>9.260002386112498</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>-13.15528867263934</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-5.837069576642584</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.1116652745247149</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.1400243166535038</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>-0.1643237404232909</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.06705710722817949</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-20,86; 3,78</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-3,67; 20,75</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-27,24; -1,7</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-17,91; 5,59</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-26,7; 6,07</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-5,34; 34,23</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-32,34; -2,31</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-19,7; 6,77</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-20.85672863304127</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-3.673054473217954</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-27.24030208056634</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-17.91092345117701</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.2670332196981846</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.05337626203655312</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.323446502767463</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.196959580696034</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>3.780690585116383</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>20.75241811364628</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>-1.698333067678413</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>5.593713250525616</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.06071760108782438</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.3422654163895338</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>-0.02306058488677622</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.06774390058855558</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>10-50.000 hab</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-5,01</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-13,96</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-2,4</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>7,36</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-6,89%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-17,75%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-3,33%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>9,32%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-14,43; 5,02</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-23,54; -5,47</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-11,94; 7,04</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-1,09; 16,04</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-18,87; 7,56</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-29,18; -7,01</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-15,84; 10,24</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-1,19; 21,8</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-5.010663808871241</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-13.95948680927336</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-2.399876638789722</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>7.362586715364172</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.06893500351693284</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.1775484827167403</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.03328731677285669</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.093162518546769</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>&gt;50.000 hab</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-1,54</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>2,98</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>6,04</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-7,56</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-2,1%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>4,13%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>8,39%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-9,53%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-14.42682569105194</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-23.5442003534142</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-11.94271208279792</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-1.089537594464013</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.1887265990108715</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.2918398749208064</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.1583810436927869</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.01191100221499502</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-13,28; 9,67</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-8,37; 14,56</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-5,69; 16,49</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-18,97; 2,48</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-16,78; 14,97</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-10,61; 22,58</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-7,2; 25,27</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-22,79; 3,08</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>5.023027927595387</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>-5.474428846811217</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>7.038842358623876</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>16.0446605137589</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.07561310705578479</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>-0.07010086917290785</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.1023752574327803</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.2180365301819808</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Capitales</t>
+          <t>&gt;50.000 hab</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +819,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-5,76</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-7,65</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-1,08</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-0,7</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-8,32%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-9,13%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-1,36%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-0,8%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-1.536965406424251</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>2.981197175707073</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>6.043153847756888</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-7.556114847989259</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.02104274708386277</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.04134896782898337</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.08390314931290609</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.09525153864465688</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-17,75; 7,28</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-17,42; 2,75</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-11,35; 7,69</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-8,96; 7,16</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-23,98; 11,12</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-20,29; 3,27</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-13,39; 10,49</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-9,95; 8,64</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-13.27663017647384</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-8.371068042462786</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-5.685767150217821</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-18.96876980396427</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.1678419963336525</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.1060816045556905</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.07196779701906569</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.2278911328835003</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>9.674142377399846</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>14.56121055206835</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>16.49249625639944</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>2.477887532393242</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.14969111510712</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.2257664221441024</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.2527133671913355</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.03082806545061705</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-5.759881935592315</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-7.646583553862918</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-1.084971934216417</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-0.703728230557954</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.08323656787255763</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.09126253830036196</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.01362188253633297</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.008000838599614628</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-17.75358067781067</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-17.41995748599064</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-11.34946394729366</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-8.962482617459196</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.2398127168568664</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.2029357037767982</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.1339056317396193</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.09945256700967924</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>7.281613248443354</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>2.747774206947216</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>7.694155669309646</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>7.164257356084512</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.1112096223909535</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.03272349804758484</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.1049481206700653</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.08643722117810175</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-5,21</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-3,85</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-2,35</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,69</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-7,3%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-5,06%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-3,09%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-0,84%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-10,68; 0,12</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-8,99; 1,63</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-7,57; 2,89</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-5,21; 4,71</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-14,6; 0,12</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-11,43; 2,29</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-9,64; 3,96</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-6,15; 5,87</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-5.212416755683913</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-3.847131579083996</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-2.346113532139593</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-0.6911477863691395</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.0730189106317876</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.0506364186767898</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.03090186111261805</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.008371939748779599</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-10.68446303506486</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-8.989965860777467</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-7.569255816311143</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-5.20983897919485</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.1460294691063848</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.1142622404113307</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.09636095031837134</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.06145701801176513</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.1205785602458333</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>1.633280847582105</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>2.890588730925806</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>4.707408935664438</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.001174760394097873</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.02290626049578703</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.03962332347630908</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.05865344595378109</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1117,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
